--- a/Excel/OutfitConfig.xlsx
+++ b/Excel/OutfitConfig.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>探险服</t>
+          <t>新手探险服</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -489,11 +489,101 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>250</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
+        <is>
+          <t>outfit_mushroom_cap</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>蘑菇采集帽</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>outfit_lantern_cloak</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>提灯斗篷</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>outfit_shop_apron</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>店长围裙</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>outfit_forest_ranger</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>森林巡游装</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>outfit_golden_chef</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>金勺厨师装</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>outfit_maze_master</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>迷宫大师套装</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>END</t>
         </is>
